--- a/artfynd/A 59566-2025 artfynd.xlsx
+++ b/artfynd/A 59566-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -892,6 +892,107 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129976956</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91602</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Högstaskogen, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>684962</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6562554</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-12-04</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 59566-2025 artfynd.xlsx
+++ b/artfynd/A 59566-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -993,6 +993,111 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129996772</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57895</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Högstaskogen, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>684910</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6562543</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 59566-2025 artfynd.xlsx
+++ b/artfynd/A 59566-2025 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>129976956</v>
       </c>
       <c r="B4" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>129996772</v>
       </c>
       <c r="B5" t="n">
-        <v>57895</v>
+        <v>57898</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 59566-2025 artfynd.xlsx
+++ b/artfynd/A 59566-2025 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>129976956</v>
       </c>
       <c r="B4" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 59566-2025 artfynd.xlsx
+++ b/artfynd/A 59566-2025 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>129976956</v>
       </c>
       <c r="B4" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>129996772</v>
       </c>
       <c r="B5" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 59566-2025 artfynd.xlsx
+++ b/artfynd/A 59566-2025 artfynd.xlsx
@@ -1692,10 +1692,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130110447</v>
+        <v>130121539</v>
       </c>
       <c r="B11" t="n">
-        <v>97705</v>
+        <v>96177</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,34 +1703,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221946</v>
+        <v>2818</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Tyresta, Tyresta, Srm</t>
+          <t>S Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>684940</v>
+        <v>684974</v>
       </c>
       <c r="R11" t="n">
-        <v>6562551</v>
+        <v>6562543</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1760,11 +1760,21 @@
           <t>2025-12-13</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-12-13</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1773,26 +1783,31 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Kraftigt nedbruten låga i kärr.</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130121539</v>
+        <v>130110447</v>
       </c>
       <c r="B12" t="n">
-        <v>96177</v>
+        <v>97705</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1800,34 +1815,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2818</v>
+        <v>221946</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>S Tyresta by, Srm</t>
+          <t>Tyresta, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>684974</v>
+        <v>684940</v>
       </c>
       <c r="R12" t="n">
-        <v>6562543</v>
+        <v>6562551</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1857,21 +1872,11 @@
           <t>2025-12-13</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>11:59</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-12-13</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>11:59</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1880,21 +1885,16 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Kraftigt nedbruten låga i kärr.</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 59566-2025 artfynd.xlsx
+++ b/artfynd/A 59566-2025 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>129976956</v>
       </c>
       <c r="B4" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1217,48 +1217,60 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130121538</v>
+        <v>130114997</v>
       </c>
       <c r="B7" t="n">
-        <v>96320</v>
+        <v>57738</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2170</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>S Tyresta by, Srm</t>
+          <t>Lingonliden2, Lingonliden2, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>684974</v>
+        <v>684941</v>
       </c>
       <c r="R7" t="n">
-        <v>6562543</v>
+        <v>6562537</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1287,7 +1299,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1297,7 +1309,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1308,81 +1320,69 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Kraftigt nedbruten låga i kärr.</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130114997</v>
+        <v>130121542</v>
       </c>
       <c r="B8" t="n">
-        <v>57738</v>
+        <v>4773</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lingonliden2, Lingonliden2, Srm</t>
+          <t>S Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>684941</v>
+        <v>684957</v>
       </c>
       <c r="R8" t="n">
-        <v>6562537</v>
+        <v>6562562</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1432,26 +1432,41 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130121542</v>
+        <v>130121538</v>
       </c>
       <c r="B9" t="n">
-        <v>4773</v>
+        <v>96322</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,39 +1474,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100299</v>
+        <v>2170</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>S Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>684957</v>
+        <v>684974</v>
       </c>
       <c r="R9" t="n">
-        <v>6562562</v>
+        <v>6562543</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,7 +1533,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1533,7 +1543,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1545,19 +1555,9 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Kraftigt nedbruten låga i kärr.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1695,7 +1695,7 @@
         <v>130121539</v>
       </c>
       <c r="B11" t="n">
-        <v>96177</v>
+        <v>96179</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v>130110447</v>
       </c>
       <c r="B12" t="n">
-        <v>97705</v>
+        <v>97707</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>130121541</v>
       </c>
       <c r="B13" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>130121534</v>
       </c>
       <c r="B14" t="n">
-        <v>92057</v>
+        <v>92059</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>130121584</v>
       </c>
       <c r="B16" t="n">
-        <v>105897</v>
+        <v>105900</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>130121578</v>
       </c>
       <c r="B17" t="n">
-        <v>91603</v>
+        <v>91605</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         <v>130121575</v>
       </c>
       <c r="B18" t="n">
-        <v>91603</v>
+        <v>91605</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>130121576</v>
       </c>
       <c r="B19" t="n">
-        <v>91603</v>
+        <v>91605</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 59566-2025 artfynd.xlsx
+++ b/artfynd/A 59566-2025 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>129976956</v>
       </c>
       <c r="B4" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>129996772</v>
       </c>
       <c r="B5" t="n">
-        <v>57900</v>
+        <v>57985</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>130121529</v>
       </c>
       <c r="B6" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1217,60 +1217,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130114997</v>
+        <v>130121538</v>
       </c>
       <c r="B7" t="n">
-        <v>57738</v>
+        <v>96409</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>2170</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lingonliden2, Lingonliden2, Srm</t>
+          <t>S Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>684941</v>
+        <v>684974</v>
       </c>
       <c r="R7" t="n">
-        <v>6562537</v>
+        <v>6562543</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1299,7 +1287,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1309,7 +1297,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1320,16 +1308,21 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Kraftigt nedbruten låga i kärr.</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1463,48 +1456,60 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130121538</v>
+        <v>130114997</v>
       </c>
       <c r="B9" t="n">
-        <v>96322</v>
+        <v>57823</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2170</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>S Tyresta by, Srm</t>
+          <t>Lingonliden2, Lingonliden2, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>684974</v>
+        <v>684941</v>
       </c>
       <c r="R9" t="n">
-        <v>6562543</v>
+        <v>6562537</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1533,7 +1538,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1543,7 +1548,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1554,21 +1559,16 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Kraftigt nedbruten låga i kärr.</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1578,7 +1578,7 @@
         <v>130121540</v>
       </c>
       <c r="B10" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         <v>130121539</v>
       </c>
       <c r="B11" t="n">
-        <v>96179</v>
+        <v>96266</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v>130110447</v>
       </c>
       <c r="B12" t="n">
-        <v>97707</v>
+        <v>97794</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>130121541</v>
       </c>
       <c r="B13" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>130121534</v>
       </c>
       <c r="B14" t="n">
-        <v>92059</v>
+        <v>92146</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>130121584</v>
       </c>
       <c r="B16" t="n">
-        <v>105900</v>
+        <v>105987</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>130121578</v>
       </c>
       <c r="B17" t="n">
-        <v>91605</v>
+        <v>91692</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         <v>130121575</v>
       </c>
       <c r="B18" t="n">
-        <v>91605</v>
+        <v>91692</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>130121576</v>
       </c>
       <c r="B19" t="n">
-        <v>91605</v>
+        <v>91692</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 59566-2025 artfynd.xlsx
+++ b/artfynd/A 59566-2025 artfynd.xlsx
@@ -1217,10 +1217,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130121538</v>
+        <v>130121542</v>
       </c>
       <c r="B7" t="n">
-        <v>96409</v>
+        <v>4773</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1228,34 +1228,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2170</v>
+        <v>100299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>S Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>684974</v>
+        <v>684957</v>
       </c>
       <c r="R7" t="n">
-        <v>6562543</v>
+        <v>6562562</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,7 +1292,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1297,7 +1302,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1309,9 +1314,19 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Kraftigt nedbruten låga i kärr.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1329,53 +1344,60 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130121542</v>
+        <v>130114997</v>
       </c>
       <c r="B8" t="n">
-        <v>4773</v>
+        <v>57823</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100299</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>S Tyresta by, Srm</t>
+          <t>Lingonliden2, Lingonliden2, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>684957</v>
+        <v>684941</v>
       </c>
       <c r="R8" t="n">
-        <v>6562562</v>
+        <v>6562537</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1404,7 +1426,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1414,7 +1436,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1425,91 +1447,64 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130114997</v>
+        <v>130121538</v>
       </c>
       <c r="B9" t="n">
-        <v>57823</v>
+        <v>96409</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>2170</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lingonliden2, Lingonliden2, Srm</t>
+          <t>S Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>684941</v>
+        <v>684974</v>
       </c>
       <c r="R9" t="n">
-        <v>6562537</v>
+        <v>6562543</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1538,7 +1533,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1548,7 +1543,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1559,16 +1554,21 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Kraftigt nedbruten låga i kärr.</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 59566-2025 artfynd.xlsx
+++ b/artfynd/A 59566-2025 artfynd.xlsx
@@ -1217,10 +1217,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130121542</v>
+        <v>130121538</v>
       </c>
       <c r="B7" t="n">
-        <v>4773</v>
+        <v>96409</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1228,39 +1228,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100299</v>
+        <v>2170</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>S Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>684957</v>
+        <v>684974</v>
       </c>
       <c r="R7" t="n">
-        <v>6562562</v>
+        <v>6562543</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,7 +1287,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1302,7 +1297,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1314,19 +1309,9 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Kraftigt nedbruten låga i kärr.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1463,10 +1448,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130121538</v>
+        <v>130121542</v>
       </c>
       <c r="B9" t="n">
-        <v>96409</v>
+        <v>4773</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1474,34 +1459,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2170</v>
+        <v>100299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>S Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>684974</v>
+        <v>684957</v>
       </c>
       <c r="R9" t="n">
-        <v>6562543</v>
+        <v>6562562</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1533,7 +1523,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1543,7 +1533,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1555,9 +1545,19 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Kraftigt nedbruten låga i kärr.</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1692,10 +1692,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130121539</v>
+        <v>130110447</v>
       </c>
       <c r="B11" t="n">
-        <v>96266</v>
+        <v>97794</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,34 +1703,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2818</v>
+        <v>221946</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>S Tyresta by, Srm</t>
+          <t>Tyresta, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>684974</v>
+        <v>684940</v>
       </c>
       <c r="R11" t="n">
-        <v>6562543</v>
+        <v>6562551</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1760,21 +1760,11 @@
           <t>2025-12-13</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>11:59</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-12-13</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>11:59</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1783,31 +1773,26 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Kraftigt nedbruten låga i kärr.</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130110447</v>
+        <v>130121539</v>
       </c>
       <c r="B12" t="n">
-        <v>97794</v>
+        <v>96266</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1815,34 +1800,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221946</v>
+        <v>2818</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Tyresta, Tyresta, Srm</t>
+          <t>S Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>684940</v>
+        <v>684974</v>
       </c>
       <c r="R12" t="n">
-        <v>6562551</v>
+        <v>6562543</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1872,11 +1857,21 @@
           <t>2025-12-13</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-12-13</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1885,16 +1880,21 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Kraftigt nedbruten låga i kärr.</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 59566-2025 artfynd.xlsx
+++ b/artfynd/A 59566-2025 artfynd.xlsx
@@ -1217,48 +1217,60 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130121538</v>
+        <v>130114997</v>
       </c>
       <c r="B7" t="n">
-        <v>96409</v>
+        <v>57823</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2170</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>S Tyresta by, Srm</t>
+          <t>Lingonliden2, Lingonliden2, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>684974</v>
+        <v>684941</v>
       </c>
       <c r="R7" t="n">
-        <v>6562543</v>
+        <v>6562537</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1287,7 +1299,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1297,7 +1309,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1308,81 +1320,64 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Kraftigt nedbruten låga i kärr.</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130114997</v>
+        <v>130121538</v>
       </c>
       <c r="B8" t="n">
-        <v>57823</v>
+        <v>96409</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>2170</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lingonliden2, Lingonliden2, Srm</t>
+          <t>S Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>684941</v>
+        <v>684974</v>
       </c>
       <c r="R8" t="n">
-        <v>6562537</v>
+        <v>6562543</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1411,7 +1406,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1421,7 +1416,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1432,16 +1427,21 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Kraftigt nedbruten låga i kärr.</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1692,10 +1692,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130110447</v>
+        <v>130121539</v>
       </c>
       <c r="B11" t="n">
-        <v>97794</v>
+        <v>96266</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,34 +1703,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221946</v>
+        <v>2818</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Tyresta, Tyresta, Srm</t>
+          <t>S Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>684940</v>
+        <v>684974</v>
       </c>
       <c r="R11" t="n">
-        <v>6562551</v>
+        <v>6562543</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1760,11 +1760,21 @@
           <t>2025-12-13</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-12-13</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1773,26 +1783,31 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Kraftigt nedbruten låga i kärr.</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130121539</v>
+        <v>130110447</v>
       </c>
       <c r="B12" t="n">
-        <v>96266</v>
+        <v>97794</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1800,34 +1815,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2818</v>
+        <v>221946</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>S Tyresta by, Srm</t>
+          <t>Tyresta, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>684974</v>
+        <v>684940</v>
       </c>
       <c r="R12" t="n">
-        <v>6562543</v>
+        <v>6562551</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1857,21 +1872,11 @@
           <t>2025-12-13</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>11:59</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-12-13</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>11:59</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1880,21 +1885,16 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Kraftigt nedbruten låga i kärr.</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2148,7 +2148,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Birgitta Tulin, Irena Koelemeijer, Ulla Sebestyen</t>
+          <t>Klas Magnusson, Ulla Sebestyen, Irena Koelemeijer, Birgitta Tulin</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 59566-2025 artfynd.xlsx
+++ b/artfynd/A 59566-2025 artfynd.xlsx
@@ -1217,48 +1217,60 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130121538</v>
+        <v>130114997</v>
       </c>
       <c r="B7" t="n">
-        <v>96409</v>
+        <v>57823</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2170</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>S Tyresta by, Srm</t>
+          <t>Lingonliden2, Lingonliden2, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>684974</v>
+        <v>684941</v>
       </c>
       <c r="R7" t="n">
-        <v>6562543</v>
+        <v>6562537</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1287,7 +1299,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1297,7 +1309,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1308,31 +1320,26 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Kraftigt nedbruten låga i kärr.</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130121542</v>
+        <v>130121538</v>
       </c>
       <c r="B8" t="n">
-        <v>4773</v>
+        <v>96412</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1340,39 +1347,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100299</v>
+        <v>2170</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>S Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>684957</v>
+        <v>684974</v>
       </c>
       <c r="R8" t="n">
-        <v>6562562</v>
+        <v>6562543</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,7 +1406,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1414,7 +1416,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1426,19 +1428,9 @@
       <c r="AG8" t="b">
         <v>0</v>
       </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Kraftigt nedbruten låga i kärr.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1456,60 +1448,53 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130114997</v>
+        <v>130121542</v>
       </c>
       <c r="B9" t="n">
-        <v>57823</v>
+        <v>4773</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lingonliden2, Lingonliden2, Srm</t>
+          <t>S Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>684941</v>
+        <v>684957</v>
       </c>
       <c r="R9" t="n">
-        <v>6562537</v>
+        <v>6562562</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1538,7 +1523,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1548,7 +1533,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1559,16 +1544,31 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1695,7 +1695,7 @@
         <v>130121539</v>
       </c>
       <c r="B11" t="n">
-        <v>96266</v>
+        <v>96269</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1807,7 +1807,7 @@
         <v>130110447</v>
       </c>
       <c r="B12" t="n">
-        <v>97794</v>
+        <v>97797</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         <v>130121541</v>
       </c>
       <c r="B13" t="n">
-        <v>91728</v>
+        <v>91731</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>130121534</v>
       </c>
       <c r="B14" t="n">
-        <v>92146</v>
+        <v>92149</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>130121584</v>
       </c>
       <c r="B16" t="n">
-        <v>105987</v>
+        <v>105990</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>130121578</v>
       </c>
       <c r="B17" t="n">
-        <v>91692</v>
+        <v>91695</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         <v>130121575</v>
       </c>
       <c r="B18" t="n">
-        <v>91692</v>
+        <v>91695</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>130121576</v>
       </c>
       <c r="B19" t="n">
-        <v>91692</v>
+        <v>91695</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 59566-2025 artfynd.xlsx
+++ b/artfynd/A 59566-2025 artfynd.xlsx
@@ -1103,7 +1103,7 @@
         <v>130121529</v>
       </c>
       <c r="B6" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>130114997</v>
       </c>
       <c r="B7" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>130121538</v>
       </c>
       <c r="B8" t="n">
-        <v>96412</v>
+        <v>96438</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
         <v>130121540</v>
       </c>
       <c r="B10" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1692,10 +1692,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130121539</v>
+        <v>130110447</v>
       </c>
       <c r="B11" t="n">
-        <v>96269</v>
+        <v>97823</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,34 +1703,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2818</v>
+        <v>221946</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>S Tyresta by, Srm</t>
+          <t>Tyresta, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>684974</v>
+        <v>684940</v>
       </c>
       <c r="R11" t="n">
-        <v>6562543</v>
+        <v>6562551</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1760,21 +1760,11 @@
           <t>2025-12-13</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>11:59</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-12-13</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>11:59</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1783,31 +1773,26 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Kraftigt nedbruten låga i kärr.</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130110447</v>
+        <v>130121539</v>
       </c>
       <c r="B12" t="n">
-        <v>97797</v>
+        <v>96295</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1815,34 +1800,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221946</v>
+        <v>2818</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Tyresta, Tyresta, Srm</t>
+          <t>S Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>684940</v>
+        <v>684974</v>
       </c>
       <c r="R12" t="n">
-        <v>6562551</v>
+        <v>6562543</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1872,11 +1857,21 @@
           <t>2025-12-13</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-12-13</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1885,16 +1880,21 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Kraftigt nedbruten låga i kärr.</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1904,7 +1904,7 @@
         <v>130121541</v>
       </c>
       <c r="B13" t="n">
-        <v>91731</v>
+        <v>91757</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>130121534</v>
       </c>
       <c r="B14" t="n">
-        <v>92149</v>
+        <v>92175</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>130121584</v>
       </c>
       <c r="B16" t="n">
-        <v>105990</v>
+        <v>106016</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2401,7 +2401,7 @@
         <v>130121578</v>
       </c>
       <c r="B17" t="n">
-        <v>91695</v>
+        <v>91721</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         <v>130121575</v>
       </c>
       <c r="B18" t="n">
-        <v>91695</v>
+        <v>91721</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>130121576</v>
       </c>
       <c r="B19" t="n">
-        <v>91695</v>
+        <v>91721</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 59566-2025 artfynd.xlsx
+++ b/artfynd/A 59566-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2915,6 +2915,228 @@
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>134440544</v>
+      </c>
+      <c r="B22" t="n">
+        <v>106317</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>N Övre Hammarby, Srm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>685174</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6562279</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ett flertal plantor varav två med blomstänglar.</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>134440598</v>
+      </c>
+      <c r="B23" t="n">
+        <v>106317</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>knoppbristning</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>N Övre Hammarby, Srm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>685131</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6562317</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ett flertal plantor varav en med blomstängel.</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 59566-2025 artfynd.xlsx
+++ b/artfynd/A 59566-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>116794459</v>
+        <v>115521296</v>
       </c>
       <c r="B2" t="n">
-        <v>56244</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,32 +686,35 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208255</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -724,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>684898</v>
+        <v>684972</v>
       </c>
       <c r="R2" t="n">
-        <v>6562545</v>
+        <v>6562517</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,12 +752,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127378764</v>
+        <v>130121537</v>
       </c>
       <c r="B3" t="n">
-        <v>56599</v>
+        <v>96554</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,43 +796,43 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208257</v>
+        <v>210</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Högstaskogen, Srm</t>
+          <t>S Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>684991</v>
+        <v>684978</v>
       </c>
       <c r="R3" t="n">
-        <v>6562475</v>
+        <v>6562526</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,12 +859,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -875,19 +883,38 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>Längst ned på kraftigt nedbruten grov granlåga.</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies # Längst ned på kraftigt nedbruten grov granlåga.</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -897,7 +924,7 @@
         <v>129976956</v>
       </c>
       <c r="B4" t="n">
-        <v>91728</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -995,10 +1022,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129996772</v>
+        <v>130111638</v>
       </c>
       <c r="B5" t="n">
-        <v>57985</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1006,45 +1033,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Högstaskogen, Srm</t>
+          <t>Lingonliden, Lingonliden, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>684910</v>
+        <v>684950</v>
       </c>
       <c r="R5" t="n">
-        <v>6562543</v>
+        <v>6562437</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1068,12 +1087,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,22 +1117,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130121529</v>
+        <v>130121541</v>
       </c>
       <c r="B6" t="n">
-        <v>57849</v>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1111,39 +1140,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>S Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>685144</v>
+        <v>684957</v>
       </c>
       <c r="R6" t="n">
-        <v>6562346</v>
+        <v>6562562</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1175,7 +1199,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1185,12 +1209,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:17</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Födosökshack vid basen av död stående tall.</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1201,6 +1220,26 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>Granlåga med barken kvar.</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga med barken kvar.</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1217,10 +1256,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130114997</v>
+        <v>130121579</v>
       </c>
       <c r="B7" t="n">
-        <v>57849</v>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1228,49 +1267,40 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lingonliden2, Lingonliden2, Srm</t>
+          <t>A 59566-2025, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>684941</v>
+        <v>684952</v>
       </c>
       <c r="R7" t="n">
-        <v>6562537</v>
+        <v>6562436</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1297,19 +1327,14 @@
           <t>2025-12-13</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-12-13</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:45</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Intressant vit svamp ovanpå som skulle kunna vara begynnande ulltickeporing (såg inga tydliga porer, så antagligen tickdyna eller någon annan generalist art), kollade på ulltickan som definitivt var död på en fallen bit av granen men ingen svamp ovanpå den.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1318,66 +1343,74 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130121538</v>
+        <v>130321608</v>
       </c>
       <c r="B8" t="n">
-        <v>96438</v>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2170</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>S Tyresta by, Srm</t>
+          <t>Skogen söder om Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>684974</v>
+        <v>684880</v>
       </c>
       <c r="R8" t="n">
-        <v>6562543</v>
+        <v>6562501</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1401,22 +1434,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>11:59</t>
+          <t>2025-12-27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>11:59</t>
+          <t>2025-12-27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1425,73 +1448,67 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Kraftigt nedbruten låga i kärr.</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Björn Persson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Björn Persson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130121542</v>
+        <v>104448489</v>
       </c>
       <c r="B9" t="n">
-        <v>4773</v>
+        <v>91923</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100299</v>
+        <v>1204</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>S Tyresta by, Srm</t>
+          <t>SSV Tyrestas viltvatten, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>684957</v>
+        <v>685006</v>
       </c>
       <c r="R9" t="n">
-        <v>6562562</v>
+        <v>6562540</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1518,22 +1535,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>11:22</t>
+          <t>2022-11-02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:22</t>
+          <t>2022-11-02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1542,83 +1549,64 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130121540</v>
+        <v>130121538</v>
       </c>
       <c r="B10" t="n">
-        <v>57849</v>
+        <v>96601</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>2170</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>S Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>684954</v>
+        <v>684974</v>
       </c>
       <c r="R10" t="n">
-        <v>6562574</v>
+        <v>6562543</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1650,7 +1638,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1660,12 +1648,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:26</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Födosökshack vid basen av död stående tall.</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1676,6 +1659,11 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Kraftigt nedbruten låga i kärr.</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1692,10 +1680,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130110447</v>
+        <v>130121591</v>
       </c>
       <c r="B11" t="n">
-        <v>97823</v>
+        <v>97394</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,37 +1691,41 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221946</v>
+        <v>2590</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Tyresta, Tyresta, Srm</t>
+          <t>S Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>684940</v>
+        <v>684947</v>
       </c>
       <c r="R11" t="n">
-        <v>6562551</v>
+        <v>6562470</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1771,28 +1763,29 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Klas Magnusson, Birgitta Tulin, Irena Koelemeijer, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130121539</v>
+        <v>130121536</v>
       </c>
       <c r="B12" t="n">
-        <v>96295</v>
+        <v>96458</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1824,10 +1817,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>684974</v>
+        <v>684978</v>
       </c>
       <c r="R12" t="n">
-        <v>6562543</v>
+        <v>6562526</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1859,7 +1852,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1869,7 +1862,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1881,9 +1874,24 @@
       <c r="AG12" t="b">
         <v>0</v>
       </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>Längst ned på kraftigt nedbruten grov granlåga.</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Kraftigt nedbruten låga i kärr.</t>
+          <t>Picea abies # Längst ned på kraftigt nedbruten grov granlåga.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1901,32 +1909,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130121541</v>
+        <v>130121539</v>
       </c>
       <c r="B13" t="n">
-        <v>91757</v>
+        <v>96458</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>2818</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1936,10 +1944,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>684957</v>
+        <v>684974</v>
       </c>
       <c r="R13" t="n">
-        <v>6562562</v>
+        <v>6562543</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1971,7 +1979,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1981,7 +1989,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1993,24 +2001,9 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL13" t="inlineStr">
-        <is>
-          <t>Granlåga med barken kvar.</t>
-        </is>
-      </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Picea abies # Granlåga med barken kvar.</t>
+          <t>Kraftigt nedbruten låga i kärr.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2028,48 +2021,48 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130121534</v>
+        <v>130121575</v>
       </c>
       <c r="B14" t="n">
-        <v>92175</v>
+        <v>91872</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6040162</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallkötticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>S Tyresta by, Srm</t>
+          <t>A 59566-2025, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>684997</v>
+        <v>684978</v>
       </c>
       <c r="R14" t="n">
-        <v>6562398</v>
+        <v>6562421</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2096,21 +2089,11 @@
           <t>2025-12-13</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-12-13</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>13:45</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2119,46 +2102,26 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL14" t="inlineStr">
-        <is>
-          <t>På gren på barklös tallåga från äldre tall.</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # På gren på barklös tallåga från äldre tall.</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Birgitta Tulin, Irena Koelemeijer, Ulla Sebestyen</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130121533</v>
+        <v>130121576</v>
       </c>
       <c r="B15" t="n">
-        <v>8451</v>
+        <v>91872</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2166,42 +2129,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>S Tyresta by, Srm</t>
+          <t>A 59566-2025, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>684997</v>
+        <v>684977</v>
       </c>
       <c r="R15" t="n">
-        <v>6562386</v>
+        <v>6562420</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2228,21 +2186,11 @@
           <t>2025-12-13</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>13:48</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-12-13</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>13:48</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2251,46 +2199,26 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL15" t="inlineStr">
-        <is>
-          <t>På gren på barklös tallåga från äldre tall.</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # På gren på barklös tallåga från äldre tall.</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130121584</v>
+        <v>130121578</v>
       </c>
       <c r="B16" t="n">
-        <v>106016</v>
+        <v>91872</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2298,42 +2226,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221144</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>A 59566-2025, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>685013</v>
+        <v>684983</v>
       </c>
       <c r="R16" t="n">
-        <v>6562405</v>
+        <v>6562551</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2368,18 +2288,12 @@
           <t>2025-12-13</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Flera plantor</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2398,10 +2312,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130121578</v>
+        <v>130009797</v>
       </c>
       <c r="B17" t="n">
-        <v>91721</v>
+        <v>57950</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2409,37 +2323,45 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>A 59566-2025, Srm</t>
+          <t>Högstaskogen, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>684983</v>
+        <v>684961</v>
       </c>
       <c r="R17" t="n">
-        <v>6562551</v>
+        <v>6562439</v>
       </c>
       <c r="S17" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2463,12 +2385,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Bearbetad granlåga, fullt av hackspån.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2483,22 +2410,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130121575</v>
+        <v>130114980</v>
       </c>
       <c r="B18" t="n">
-        <v>91721</v>
+        <v>57950</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2506,37 +2433,49 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>A 59566-2025, Srm</t>
+          <t>Lingonliden2, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>684978</v>
+        <v>684878</v>
       </c>
       <c r="R18" t="n">
-        <v>6562421</v>
+        <v>6562610</v>
       </c>
       <c r="S18" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2563,9 +2502,19 @@
           <t>2025-12-13</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2580,22 +2529,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130121576</v>
+        <v>130114997</v>
       </c>
       <c r="B19" t="n">
-        <v>91721</v>
+        <v>57950</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2603,37 +2552,49 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>A 59566-2025, Srm</t>
+          <t>Lingonliden2, Lingonliden2, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>684977</v>
+        <v>684941</v>
       </c>
       <c r="R19" t="n">
-        <v>6562420</v>
+        <v>6562537</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2660,9 +2621,19 @@
           <t>2025-12-13</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2677,22 +2648,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133964707</v>
+        <v>130121529</v>
       </c>
       <c r="B20" t="n">
-        <v>56896</v>
+        <v>57950</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2700,47 +2671,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>208257</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>funnen död</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Högstaskogen, Srm</t>
+          <t>S Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>684926</v>
+        <v>685144</v>
       </c>
       <c r="R20" t="n">
-        <v>6562530</v>
+        <v>6562346</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2767,17 +2730,27 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På ridvägen med krossat huvud.</t>
+          <t>Födosökshack vid basen av död stående tall.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2786,29 +2759,28 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134003472</v>
+        <v>130121540</v>
       </c>
       <c r="B21" t="n">
-        <v>56896</v>
+        <v>57950</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2816,43 +2788,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>208257</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Högstaskogen, Srm</t>
+          <t>S Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>684886</v>
+        <v>684954</v>
       </c>
       <c r="R21" t="n">
-        <v>6562537</v>
+        <v>6562574</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2879,17 +2847,27 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På ridvägen.</t>
+          <t>Födosökshack vid basen av död stående tall.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2898,29 +2876,28 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134440544</v>
+        <v>130121542</v>
       </c>
       <c r="B22" t="n">
-        <v>106317</v>
+        <v>4775</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2928,42 +2905,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221144</v>
+        <v>100299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>N Övre Hammarby, Srm</t>
+          <t>S Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>685174</v>
+        <v>684957</v>
       </c>
       <c r="R22" t="n">
-        <v>6562279</v>
+        <v>6562562</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2990,17 +2964,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ett flertal plantor varav två med blomstänglar.</t>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3009,29 +2988,43 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134440598</v>
+        <v>130121544</v>
       </c>
       <c r="B23" t="n">
-        <v>106317</v>
+        <v>4775</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3039,42 +3032,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221144</v>
+        <v>100299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>knoppbristning</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>N Övre Hammarby, Srm</t>
+          <t>S Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>685131</v>
+        <v>684893</v>
       </c>
       <c r="R23" t="n">
-        <v>6562317</v>
+        <v>6562601</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3101,17 +3091,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ett flertal plantor varav en med blomstängel.</t>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3120,22 +3115,2831 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>130121543</v>
+      </c>
+      <c r="B24" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>S Tyresta by, Srm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>684897</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6562616</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>130115019</v>
+      </c>
+      <c r="B25" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Lingonliden2, Srm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>684878</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6562610</v>
+      </c>
+      <c r="S25" t="n">
+        <v>8</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Anneli Ahlroth</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Anneli Ahlroth</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>129996772</v>
+      </c>
+      <c r="B26" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Högstaskogen, Srm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>684910</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6562543</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
           <t>Bodil Ravn</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
+      <c r="AX26" t="inlineStr">
         <is>
           <t>Bodil Ravn</t>
         </is>
       </c>
-      <c r="AY23" t="inlineStr"/>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>130115016</v>
+      </c>
+      <c r="B27" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Lingonliden2, Srm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>684878</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6562610</v>
+      </c>
+      <c r="S27" t="n">
+        <v>8</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Anneli Ahlroth</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Anneli Ahlroth</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>130328801</v>
+      </c>
+      <c r="B28" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Högstaskogen, Srm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>684955</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6562389</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-12-28</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>134179933</v>
+      </c>
+      <c r="B29" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Högstaskogen, Srm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>684976</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6562378</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>134180019</v>
+      </c>
+      <c r="B30" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Högstaskogen, Srm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>685035</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6562398</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>130114978</v>
+      </c>
+      <c r="B31" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Lingonliden2, Lingonliden2, Srm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>685149</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6562238</v>
+      </c>
+      <c r="S31" t="n">
+        <v>17</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Anneli Ahlroth</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Anneli Ahlroth, Irena Koelemeijer</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>130121530</v>
+      </c>
+      <c r="B32" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>S Tyresta by, Srm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>685150</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6562245</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL32" t="inlineStr">
+        <is>
+          <t>Tallåga</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Tallåga</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>130121533</v>
+      </c>
+      <c r="B33" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>S Tyresta by, Srm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>684997</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6562386</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL33" t="inlineStr">
+        <is>
+          <t>På gren på barklös tallåga från äldre tall.</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # På gren på barklös tallåga från äldre tall.</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>130330908</v>
+      </c>
+      <c r="B34" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Skogen söder om Tyresta by, Srm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>684899</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6562614</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-12-27</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-12-27</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Björn Persson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Björn Persson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>116794459</v>
+      </c>
+      <c r="B35" t="n">
+        <v>56884</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>208255</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Skogsödla</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Zootoca vivipara</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Jacquin, 1787)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Högstaskogen, Srm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>684898</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6562545</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-05-10</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>127378764</v>
+      </c>
+      <c r="B36" t="n">
+        <v>56876</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>208257</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Kopparödla</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Anguis fragilis</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Högstaskogen, Srm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>684991</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6562475</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-08-10</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>133964707</v>
+      </c>
+      <c r="B37" t="n">
+        <v>56896</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>208257</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Kopparödla</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Anguis fragilis</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>funnen död</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Högstaskogen, Srm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>684926</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6562530</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>På ridvägen med krossat huvud.</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>134003472</v>
+      </c>
+      <c r="B38" t="n">
+        <v>56896</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>208257</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Kopparödla</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Anguis fragilis</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Högstaskogen, Srm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>684886</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6562537</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På ridvägen.</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>133965707</v>
+      </c>
+      <c r="B39" t="n">
+        <v>98219</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>219815</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Ekbräken</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Gymnocarpium dryopteris</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) Newman</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>N Övre Hammarby, Srm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>685126</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6562254</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>115521263</v>
+      </c>
+      <c r="B40" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Högstaskogen, Srm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>684827</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6562598</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-03-23</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-03-23</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>130121584</v>
+      </c>
+      <c r="B41" t="n">
+        <v>106243</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>A 59566-2025, Srm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>685013</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6562405</v>
+      </c>
+      <c r="S41" t="n">
+        <v>4</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Flera plantor</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="inlineStr"/>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>134440544</v>
+      </c>
+      <c r="B42" t="n">
+        <v>106324</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>N Övre Hammarby, Srm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>685174</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6562279</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ett flertal plantor varav två med blomstänglar.</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>134440598</v>
+      </c>
+      <c r="B43" t="n">
+        <v>106324</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>knoppbristning</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>N Övre Hammarby, Srm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>685131</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6562317</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ett flertal plantor varav en med blomstängel.</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>130121531</v>
+      </c>
+      <c r="B44" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>S Tyresta by, Srm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>685093</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6562301</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>130110447</v>
+      </c>
+      <c r="B45" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Tyresta, Tyresta, Srm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>684940</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6562551</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Måns Persson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Måns Persson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>130115022</v>
+      </c>
+      <c r="B46" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Lingonliden2, Srm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>684878</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6562610</v>
+      </c>
+      <c r="S46" t="n">
+        <v>8</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Anneli Ahlroth</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Anneli Ahlroth</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>133965744</v>
+      </c>
+      <c r="B47" t="n">
+        <v>98249</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>N Övre Hammarby, Srm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>685126</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6562254</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="inlineStr"/>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>130121534</v>
+      </c>
+      <c r="B48" t="n">
+        <v>92328</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6040162</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Tallkötticka</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Leptoporus erubescens</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>S Tyresta by, Srm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>684997</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6562398</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL48" t="inlineStr">
+        <is>
+          <t>På gren på barklös tallåga från äldre tall.</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # På gren på barklös tallåga från äldre tall.</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Birgitta Tulin, Irena Koelemeijer, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 59566-2025 artfynd.xlsx
+++ b/artfynd/A 59566-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY48"/>
+  <dimension ref="A1:AY49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1568,45 +1568,52 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130121538</v>
+        <v>135324359</v>
       </c>
       <c r="B10" t="n">
-        <v>96601</v>
+        <v>91459</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2170</v>
+        <v>2051</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>Kytöv. &amp; M.Toivonen</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>S Tyresta by, Srm</t>
+          <t>N Övre Hammarby, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>684974</v>
+        <v>685200</v>
       </c>
       <c r="R10" t="n">
-        <v>6562543</v>
+        <v>6562241</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1633,22 +1640,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>11:59</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>11:59</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1657,33 +1654,29 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Kraftigt nedbruten låga i kärr.</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130121591</v>
+        <v>130121538</v>
       </c>
       <c r="B11" t="n">
-        <v>97394</v>
+        <v>96601</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1691,41 +1684,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2590</v>
+        <v>2170</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>S Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>684947</v>
+        <v>684974</v>
       </c>
       <c r="R11" t="n">
-        <v>6562470</v>
+        <v>6562543</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1752,20 +1741,34 @@
           <t>2025-12-13</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-12-13</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Kraftigt nedbruten låga i kärr.</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1775,17 +1778,17 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Birgitta Tulin, Irena Koelemeijer, Ulla Sebestyen</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130121536</v>
+        <v>130121591</v>
       </c>
       <c r="B12" t="n">
-        <v>96458</v>
+        <v>97394</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1793,37 +1796,41 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2818</v>
+        <v>2590</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>S Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>684978</v>
+        <v>684947</v>
       </c>
       <c r="R12" t="n">
-        <v>6562526</v>
+        <v>6562470</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1850,49 +1857,20 @@
           <t>2025-12-13</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>12:02</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-12-13</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>12:02</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>Längst ned på kraftigt nedbruten grov granlåga.</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Picea abies # Längst ned på kraftigt nedbruten grov granlåga.</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1902,14 +1880,14 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Birgitta Tulin, Irena Koelemeijer, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130121539</v>
+        <v>130121536</v>
       </c>
       <c r="B13" t="n">
         <v>96458</v>
@@ -1944,10 +1922,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>684974</v>
+        <v>684978</v>
       </c>
       <c r="R13" t="n">
-        <v>6562543</v>
+        <v>6562526</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1979,7 +1957,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1989,7 +1967,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2001,9 +1979,24 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>Längst ned på kraftigt nedbruten grov granlåga.</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Kraftigt nedbruten låga i kärr.</t>
+          <t>Picea abies # Längst ned på kraftigt nedbruten grov granlåga.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2021,10 +2014,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130121575</v>
+        <v>130121539</v>
       </c>
       <c r="B14" t="n">
-        <v>91872</v>
+        <v>96458</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2032,37 +2025,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>2818</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>A 59566-2025, Srm</t>
+          <t>S Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>684978</v>
+        <v>684974</v>
       </c>
       <c r="R14" t="n">
-        <v>6562421</v>
+        <v>6562543</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2089,11 +2082,21 @@
           <t>2025-12-13</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-12-13</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2102,23 +2105,28 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Kraftigt nedbruten låga i kärr.</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130121576</v>
+        <v>130121575</v>
       </c>
       <c r="B15" t="n">
         <v>91872</v>
@@ -2153,10 +2161,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>684977</v>
+        <v>684978</v>
       </c>
       <c r="R15" t="n">
-        <v>6562420</v>
+        <v>6562421</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2215,7 +2223,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130121578</v>
+        <v>130121576</v>
       </c>
       <c r="B16" t="n">
         <v>91872</v>
@@ -2250,10 +2258,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>684983</v>
+        <v>684977</v>
       </c>
       <c r="R16" t="n">
-        <v>6562551</v>
+        <v>6562420</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2312,10 +2320,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130009797</v>
+        <v>130121578</v>
       </c>
       <c r="B17" t="n">
-        <v>57950</v>
+        <v>91872</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2323,45 +2331,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Högstaskogen, Srm</t>
+          <t>A 59566-2025, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>684961</v>
+        <v>684983</v>
       </c>
       <c r="R17" t="n">
-        <v>6562439</v>
+        <v>6562551</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2385,17 +2385,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Bearbetad granlåga, fullt av hackspån.</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2410,19 +2405,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130114980</v>
+        <v>130009797</v>
       </c>
       <c r="B18" t="n">
         <v>57950</v>
@@ -2450,11 +2445,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
@@ -2465,17 +2456,17 @@
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lingonliden2, Srm</t>
+          <t>Högstaskogen, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>684878</v>
+        <v>684961</v>
       </c>
       <c r="R18" t="n">
-        <v>6562610</v>
+        <v>6562439</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2499,22 +2490,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>11:31</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>11:31</t>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Bearbetad granlåga, fullt av hackspån.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2529,19 +2515,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130114997</v>
+        <v>130114980</v>
       </c>
       <c r="B19" t="n">
         <v>57950</v>
@@ -2584,14 +2570,14 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lingonliden2, Lingonliden2, Srm</t>
+          <t>Lingonliden2, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>684941</v>
+        <v>684878</v>
       </c>
       <c r="R19" t="n">
-        <v>6562537</v>
+        <v>6562610</v>
       </c>
       <c r="S19" t="n">
         <v>8</v>
@@ -2623,7 +2609,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2633,7 +2619,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2660,7 +2646,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130121529</v>
+        <v>130114997</v>
       </c>
       <c r="B20" t="n">
         <v>57950</v>
@@ -2688,25 +2674,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>S Tyresta by, Srm</t>
+          <t>Lingonliden2, Lingonliden2, Srm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>685144</v>
+        <v>684941</v>
       </c>
       <c r="R20" t="n">
-        <v>6562346</v>
+        <v>6562537</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2735,7 +2728,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2745,12 +2738,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:17</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Födosökshack vid basen av död stående tall.</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2765,19 +2753,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130121540</v>
+        <v>130121529</v>
       </c>
       <c r="B21" t="n">
         <v>57950</v>
@@ -2817,10 +2805,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>684954</v>
+        <v>685144</v>
       </c>
       <c r="R21" t="n">
-        <v>6562574</v>
+        <v>6562346</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2852,7 +2840,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2862,7 +2850,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -2894,10 +2882,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130121542</v>
+        <v>130121540</v>
       </c>
       <c r="B22" t="n">
-        <v>4775</v>
+        <v>57950</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2905,27 +2893,27 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100299</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2934,10 +2922,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>684957</v>
+        <v>684954</v>
       </c>
       <c r="R22" t="n">
-        <v>6562562</v>
+        <v>6562574</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2969,7 +2957,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2979,7 +2967,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Födosökshack vid basen av död stående tall.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2990,21 +2983,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3021,7 +2999,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130121544</v>
+        <v>130121542</v>
       </c>
       <c r="B23" t="n">
         <v>4775</v>
@@ -3061,10 +3039,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>684893</v>
+        <v>684957</v>
       </c>
       <c r="R23" t="n">
-        <v>6562601</v>
+        <v>6562562</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3096,7 +3074,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3106,7 +3084,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3148,10 +3126,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130121543</v>
+        <v>130121544</v>
       </c>
       <c r="B24" t="n">
-        <v>5179</v>
+        <v>4775</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3159,21 +3137,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3188,10 +3166,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>684897</v>
+        <v>684893</v>
       </c>
       <c r="R24" t="n">
-        <v>6562616</v>
+        <v>6562601</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3223,7 +3201,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3233,7 +3211,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3275,10 +3253,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130115019</v>
+        <v>130121543</v>
       </c>
       <c r="B25" t="n">
-        <v>58327</v>
+        <v>5179</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3286,49 +3264,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103015</v>
+        <v>100526</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lingonliden2, Srm</t>
+          <t>S Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>684878</v>
+        <v>684897</v>
       </c>
       <c r="R25" t="n">
-        <v>6562610</v>
+        <v>6562616</v>
       </c>
       <c r="S25" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3357,7 +3328,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3367,7 +3338,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3378,72 +3349,91 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129996772</v>
+        <v>130115019</v>
       </c>
       <c r="B26" t="n">
-        <v>58114</v>
+        <v>58327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Högstaskogen, Srm</t>
+          <t>Lingonliden2, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>684910</v>
+        <v>684878</v>
       </c>
       <c r="R26" t="n">
-        <v>6562543</v>
+        <v>6562610</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3467,12 +3457,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3487,19 +3487,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130115016</v>
+        <v>129996772</v>
       </c>
       <c r="B27" t="n">
         <v>58114</v>
@@ -3527,32 +3527,28 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lingonliden2, Srm</t>
+          <t>Högstaskogen, Srm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>684878</v>
+        <v>684910</v>
       </c>
       <c r="R27" t="n">
-        <v>6562610</v>
+        <v>6562543</v>
       </c>
       <c r="S27" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3576,22 +3572,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>11:02</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>11:02</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3606,19 +3592,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130328801</v>
+        <v>130115016</v>
       </c>
       <c r="B28" t="n">
         <v>58114</v>
@@ -3646,28 +3632,32 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Högstaskogen, Srm</t>
+          <t>Lingonliden2, Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>684955</v>
+        <v>684878</v>
       </c>
       <c r="R28" t="n">
-        <v>6562389</v>
+        <v>6562610</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3691,12 +3681,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3711,22 +3711,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134179933</v>
+        <v>130328801</v>
       </c>
       <c r="B29" t="n">
-        <v>58136</v>
+        <v>58114</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -3766,13 +3766,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>684976</v>
+        <v>684955</v>
       </c>
       <c r="R29" t="n">
-        <v>6562378</v>
+        <v>6562389</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3796,12 +3796,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3828,7 +3828,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134180019</v>
+        <v>134179933</v>
       </c>
       <c r="B30" t="n">
         <v>58136</v>
@@ -3871,10 +3871,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>685035</v>
+        <v>684976</v>
       </c>
       <c r="R30" t="n">
-        <v>6562398</v>
+        <v>6562378</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3933,57 +3933,56 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130114978</v>
+        <v>134180019</v>
       </c>
       <c r="B31" t="n">
-        <v>8455</v>
+        <v>58136</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lingonliden2, Lingonliden2, Srm</t>
+          <t>Högstaskogen, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>685149</v>
+        <v>685035</v>
       </c>
       <c r="R31" t="n">
-        <v>6562238</v>
+        <v>6562398</v>
       </c>
       <c r="S31" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4007,22 +4006,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>14:04</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>14:04</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4037,19 +4026,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth, Irena Koelemeijer</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130121530</v>
+        <v>130114978</v>
       </c>
       <c r="B32" t="n">
         <v>8455</v>
@@ -4077,25 +4066,29 @@
           <t>(Hartig, 1834)</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>S Tyresta by, Srm</t>
+          <t>Lingonliden2, Lingonliden2, Srm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>685150</v>
+        <v>685149</v>
       </c>
       <c r="R32" t="n">
-        <v>6562245</v>
+        <v>6562238</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4124,7 +4117,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4134,7 +4127,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4145,43 +4138,23 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL32" t="inlineStr">
-        <is>
-          <t>Tallåga</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Tallåga</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Anneli Ahlroth, Irena Koelemeijer</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130121533</v>
+        <v>130121530</v>
       </c>
       <c r="B33" t="n">
         <v>8455</v>
@@ -4221,10 +4194,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>684997</v>
+        <v>685150</v>
       </c>
       <c r="R33" t="n">
-        <v>6562386</v>
+        <v>6562245</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4256,7 +4229,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4266,7 +4239,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4290,12 +4263,12 @@
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>På gren på barklös tallåga från äldre tall.</t>
+          <t>Tallåga</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # På gren på barklös tallåga från äldre tall.</t>
+          <t>Pinus sylvestris # Tallåga</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4313,7 +4286,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130330908</v>
+        <v>130121533</v>
       </c>
       <c r="B34" t="n">
         <v>8455</v>
@@ -4342,25 +4315,21 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Skogen söder om Tyresta by, Srm</t>
+          <t>S Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>684899</v>
+        <v>684997</v>
       </c>
       <c r="R34" t="n">
-        <v>6562614</v>
+        <v>6562386</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4387,12 +4356,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4401,29 +4380,48 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL34" t="inlineStr">
+        <is>
+          <t>På gren på barklös tallåga från äldre tall.</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # På gren på barklös tallåga från äldre tall.</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Björn Persson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Björn Persson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>116794459</v>
+        <v>130330908</v>
       </c>
       <c r="B35" t="n">
-        <v>56884</v>
+        <v>8455</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4431,43 +4429,43 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>208255</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Högstaskogen, Srm</t>
+          <t>Skogen söder om Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>684898</v>
+        <v>684899</v>
       </c>
       <c r="R35" t="n">
-        <v>6562545</v>
+        <v>6562614</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4494,12 +4492,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2025-12-27</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2025-12-27</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4515,22 +4513,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Björn Persson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Björn Persson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127378764</v>
+        <v>116794459</v>
       </c>
       <c r="B36" t="n">
-        <v>56876</v>
+        <v>56884</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4538,21 +4536,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>208257</v>
+        <v>208255</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4571,10 +4569,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>684991</v>
+        <v>684898</v>
       </c>
       <c r="R36" t="n">
-        <v>6562475</v>
+        <v>6562545</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4601,12 +4599,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2024-05-10</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2024-05-10</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4634,10 +4632,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133964707</v>
+        <v>127378764</v>
       </c>
       <c r="B37" t="n">
-        <v>56896</v>
+        <v>56876</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4670,11 +4668,7 @@
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>funnen död</t>
-        </is>
-      </c>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4682,10 +4676,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>684926</v>
+        <v>684991</v>
       </c>
       <c r="R37" t="n">
-        <v>6562530</v>
+        <v>6562475</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4712,17 +4706,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>På ridvägen med krossat huvud.</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4750,7 +4739,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>134003472</v>
+        <v>133964707</v>
       </c>
       <c r="B38" t="n">
         <v>56896</v>
@@ -4786,7 +4775,11 @@
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>funnen död</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4794,10 +4787,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>684886</v>
+        <v>684926</v>
       </c>
       <c r="R38" t="n">
-        <v>6562537</v>
+        <v>6562530</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4824,17 +4817,17 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På ridvägen.</t>
+          <t>På ridvägen med krossat huvud.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4862,10 +4855,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133965707</v>
+        <v>134003472</v>
       </c>
       <c r="B39" t="n">
-        <v>98219</v>
+        <v>56896</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4873,38 +4866,43 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>219815</v>
+        <v>208257</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ekbräken</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Gymnocarpium dryopteris</t>
+          <t>Anguis fragilis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Newman</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>N Övre Hammarby, Srm</t>
+          <t>Högstaskogen, Srm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>685126</v>
+        <v>684886</v>
       </c>
       <c r="R39" t="n">
-        <v>6562254</v>
+        <v>6562537</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4931,12 +4929,17 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>På ridvägen.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4964,10 +4967,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>115521263</v>
+        <v>133965707</v>
       </c>
       <c r="B40" t="n">
-        <v>106244</v>
+        <v>98219</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4975,21 +4978,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221144</v>
+        <v>219815</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Newman</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4999,14 +5002,14 @@
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Högstaskogen, Srm</t>
+          <t>N Övre Hammarby, Srm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>684827</v>
+        <v>685126</v>
       </c>
       <c r="R40" t="n">
-        <v>6562598</v>
+        <v>6562254</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5033,12 +5036,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5066,10 +5069,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130121584</v>
+        <v>115521263</v>
       </c>
       <c r="B41" t="n">
-        <v>106243</v>
+        <v>106244</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5096,26 +5099,22 @@
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>A 59566-2025, Srm</t>
+          <t>Högstaskogen, Srm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>685013</v>
+        <v>684827</v>
       </c>
       <c r="R41" t="n">
-        <v>6562405</v>
+        <v>6562598</v>
       </c>
       <c r="S41" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5139,17 +5138,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Flera plantor</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5165,22 +5159,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>134440544</v>
+        <v>130121584</v>
       </c>
       <c r="B42" t="n">
-        <v>106324</v>
+        <v>106243</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5209,24 +5203,24 @@
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>N Övre Hammarby, Srm</t>
+          <t>A 59566-2025, Srm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>685174</v>
+        <v>685013</v>
       </c>
       <c r="R42" t="n">
-        <v>6562279</v>
+        <v>6562405</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5250,17 +5244,17 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ett flertal plantor varav två med blomstänglar.</t>
+          <t>Flera plantor</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5276,19 +5270,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>134440598</v>
+        <v>134440544</v>
       </c>
       <c r="B43" t="n">
         <v>106324</v>
@@ -5320,7 +5314,7 @@
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>knoppbristning</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
@@ -5331,10 +5325,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>685131</v>
+        <v>685174</v>
       </c>
       <c r="R43" t="n">
-        <v>6562317</v>
+        <v>6562279</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5371,7 +5365,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ett flertal plantor varav en med blomstängel.</t>
+          <t>Ett flertal plantor varav två med blomstänglar.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5399,10 +5393,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130121531</v>
+        <v>134440598</v>
       </c>
       <c r="B44" t="n">
-        <v>97983</v>
+        <v>106324</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5410,34 +5404,42 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221945</v>
+        <v>221144</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>knoppbristning</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>S Tyresta by, Srm</t>
+          <t>N Övre Hammarby, Srm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>685093</v>
+        <v>685131</v>
       </c>
       <c r="R44" t="n">
-        <v>6562301</v>
+        <v>6562317</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5464,22 +5466,17 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>13:53</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>13:53</t>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ett flertal plantor varav en med blomstängel.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5488,28 +5485,29 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130110447</v>
+        <v>130121531</v>
       </c>
       <c r="B45" t="n">
-        <v>97986</v>
+        <v>97983</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5517,16 +5515,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5537,14 +5535,14 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Tyresta, Tyresta, Srm</t>
+          <t>S Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>684940</v>
+        <v>685093</v>
       </c>
       <c r="R45" t="n">
-        <v>6562551</v>
+        <v>6562301</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5574,9 +5572,19 @@
           <t>2025-12-13</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5591,19 +5599,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130115022</v>
+        <v>130110447</v>
       </c>
       <c r="B46" t="n">
         <v>97986</v>
@@ -5632,23 +5640,19 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lingonliden2, Srm</t>
+          <t>Tyresta, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>684878</v>
+        <v>684940</v>
       </c>
       <c r="R46" t="n">
-        <v>6562610</v>
+        <v>6562551</v>
       </c>
       <c r="S46" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5675,19 +5679,9 @@
           <t>2025-12-13</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>11:22</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>11:22</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5702,22 +5696,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133965744</v>
+        <v>130115022</v>
       </c>
       <c r="B47" t="n">
-        <v>98249</v>
+        <v>97986</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5725,21 +5719,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>223358</v>
+        <v>221946</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5749,17 +5743,17 @@
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>N Övre Hammarby, Srm</t>
+          <t>Lingonliden2, Srm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>685126</v>
+        <v>684878</v>
       </c>
       <c r="R47" t="n">
-        <v>6562254</v>
+        <v>6562610</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5783,12 +5777,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5797,64 +5801,67 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130121534</v>
+        <v>133965744</v>
       </c>
       <c r="B48" t="n">
-        <v>92328</v>
+        <v>98249</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6040162</v>
+        <v>223358</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tallkötticka</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>S Tyresta by, Srm</t>
+          <t>N Övre Hammarby, Srm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>684997</v>
+        <v>685126</v>
       </c>
       <c r="R48" t="n">
-        <v>6562398</v>
+        <v>6562254</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5881,22 +5888,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>13:45</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>13:45</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5905,41 +5902,149 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL48" t="inlineStr">
-        <is>
-          <t>På gren på barklös tallåga från äldre tall.</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # På gren på barklös tallåga från äldre tall.</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>130121534</v>
+      </c>
+      <c r="B49" t="n">
+        <v>92328</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6040162</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Tallkötticka</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Leptoporus erubescens</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>S Tyresta by, Srm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>684997</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6562398</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL49" t="inlineStr">
+        <is>
+          <t>På gren på barklös tallåga från äldre tall.</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # På gren på barklös tallåga från äldre tall.</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
           <t>Klas Magnusson</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
+      <c r="AX49" t="inlineStr">
         <is>
           <t>Klas Magnusson, Birgitta Tulin, Irena Koelemeijer, Ulla Sebestyen</t>
         </is>
       </c>
-      <c r="AY48" t="inlineStr"/>
+      <c r="AY49" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 59566-2025 artfynd.xlsx
+++ b/artfynd/A 59566-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY49"/>
+  <dimension ref="A1:AZ49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115521296</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -918,6 +928,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130121537</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1019,6 +1034,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129976956</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1126,6 +1146,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130111638</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1253,6 +1278,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130121541</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1359,6 +1389,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130121579</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1464,6 +1499,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130321608</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1565,6 +1605,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104448489</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1670,6 +1715,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135324359</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1782,6 +1832,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130121538</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1884,6 +1939,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130121591</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2011,6 +2071,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130121536</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2123,6 +2188,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130121539</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2220,6 +2290,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130121575</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2317,6 +2392,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130121576</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2414,6 +2494,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130121578</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2524,6 +2609,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130009797</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2643,6 +2733,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130114980</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2762,6 +2857,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130114997</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2879,6 +2979,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130121529</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2996,6 +3101,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130121540</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3123,6 +3233,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130121542</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3250,6 +3365,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130121544</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3377,6 +3497,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130121543</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3496,6 +3621,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130115019</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3601,6 +3731,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129996772</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3720,6 +3855,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130115016</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3825,6 +3965,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130328801</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3930,6 +4075,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134179933</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4035,6 +4185,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134180019</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4151,6 +4306,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130114978</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4283,6 +4443,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130121530</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4415,6 +4580,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130121533</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4522,6 +4692,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130330908</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4629,6 +4804,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116794459</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4736,6 +4916,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127378764</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4852,6 +5037,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133964707</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4964,6 +5154,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134003472</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5066,6 +5261,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965707</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5168,6 +5368,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115521263</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5279,6 +5484,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130121584</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5390,6 +5600,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134440544</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5501,6 +5716,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134440598</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5608,6 +5828,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130121531</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5705,6 +5930,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130110447</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5816,6 +6046,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130115022</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5918,6 +6153,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965744</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6045,8 +6285,63 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130121534</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 59566-2025 artfynd.xlsx
+++ b/artfynd/A 59566-2025 artfynd.xlsx
@@ -1616,7 +1616,7 @@
         <v>135324359</v>
       </c>
       <c r="B10" t="n">
-        <v>91459</v>
+        <v>91501</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 59566-2025 artfynd.xlsx
+++ b/artfynd/A 59566-2025 artfynd.xlsx
@@ -1616,7 +1616,7 @@
         <v>135324359</v>
       </c>
       <c r="B10" t="n">
-        <v>91501</v>
+        <v>91528</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 59566-2025 artfynd.xlsx
+++ b/artfynd/A 59566-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ48"/>
+  <dimension ref="A1:AZ49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1613,45 +1613,52 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130121538</v>
+        <v>135324359</v>
       </c>
       <c r="B10" t="n">
-        <v>96601</v>
+        <v>91531</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2170</v>
+        <v>2051</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>Kytöv. &amp; M.Toivonen</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>S Tyresta by, Srm</t>
+          <t>N Övre Hammarby, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>684974</v>
+        <v>685200</v>
       </c>
       <c r="R10" t="n">
-        <v>6562543</v>
+        <v>6562241</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1678,22 +1685,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>11:59</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>11:59</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1702,38 +1699,34 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Kraftigt nedbruten låga i kärr.</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130121538</t>
+          <t>https://artportalen.se/Sighting/135324359</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130121591</v>
+        <v>130121538</v>
       </c>
       <c r="B11" t="n">
-        <v>97394</v>
+        <v>96601</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1741,41 +1734,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2590</v>
+        <v>2170</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>S Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>684947</v>
+        <v>684974</v>
       </c>
       <c r="R11" t="n">
-        <v>6562470</v>
+        <v>6562543</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1802,20 +1791,34 @@
           <t>2025-12-13</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-12-13</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Kraftigt nedbruten låga i kärr.</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1825,22 +1828,22 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Birgitta Tulin, Irena Koelemeijer, Ulla Sebestyen</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130121591</t>
+          <t>https://artportalen.se/Sighting/130121538</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130121536</v>
+        <v>130121591</v>
       </c>
       <c r="B12" t="n">
-        <v>96458</v>
+        <v>97394</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1848,37 +1851,41 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2818</v>
+        <v>2590</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>S Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>684978</v>
+        <v>684947</v>
       </c>
       <c r="R12" t="n">
-        <v>6562526</v>
+        <v>6562470</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1905,49 +1912,20 @@
           <t>2025-12-13</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>12:02</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-12-13</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>12:02</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>Längst ned på kraftigt nedbruten grov granlåga.</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Picea abies # Längst ned på kraftigt nedbruten grov granlåga.</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1957,19 +1935,19 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Klas Magnusson, Birgitta Tulin, Irena Koelemeijer, Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130121536</t>
+          <t>https://artportalen.se/Sighting/130121591</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130121539</v>
+        <v>130121536</v>
       </c>
       <c r="B13" t="n">
         <v>96458</v>
@@ -2004,10 +1982,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>684974</v>
+        <v>684978</v>
       </c>
       <c r="R13" t="n">
-        <v>6562543</v>
+        <v>6562526</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2039,7 +2017,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2049,7 +2027,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2061,9 +2039,24 @@
       <c r="AG13" t="b">
         <v>0</v>
       </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>Längst ned på kraftigt nedbruten grov granlåga.</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Kraftigt nedbruten låga i kärr.</t>
+          <t>Picea abies # Längst ned på kraftigt nedbruten grov granlåga.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2080,16 +2073,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130121539</t>
+          <t>https://artportalen.se/Sighting/130121536</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130121575</v>
+        <v>130121539</v>
       </c>
       <c r="B14" t="n">
-        <v>91872</v>
+        <v>96458</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2097,37 +2090,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>2818</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>A 59566-2025, Srm</t>
+          <t>S Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>684978</v>
+        <v>684974</v>
       </c>
       <c r="R14" t="n">
-        <v>6562421</v>
+        <v>6562543</v>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2154,11 +2147,21 @@
           <t>2025-12-13</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-12-13</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2167,28 +2170,33 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Kraftigt nedbruten låga i kärr.</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130121575</t>
+          <t>https://artportalen.se/Sighting/130121539</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130121576</v>
+        <v>130121575</v>
       </c>
       <c r="B15" t="n">
         <v>91872</v>
@@ -2223,10 +2231,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>684977</v>
+        <v>684978</v>
       </c>
       <c r="R15" t="n">
-        <v>6562420</v>
+        <v>6562421</v>
       </c>
       <c r="S15" t="n">
         <v>4</v>
@@ -2284,13 +2292,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130121576</t>
+          <t>https://artportalen.se/Sighting/130121575</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130121578</v>
+        <v>130121576</v>
       </c>
       <c r="B16" t="n">
         <v>91872</v>
@@ -2325,10 +2333,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>684983</v>
+        <v>684977</v>
       </c>
       <c r="R16" t="n">
-        <v>6562551</v>
+        <v>6562420</v>
       </c>
       <c r="S16" t="n">
         <v>4</v>
@@ -2386,16 +2394,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130121578</t>
+          <t>https://artportalen.se/Sighting/130121576</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130009797</v>
+        <v>130121578</v>
       </c>
       <c r="B17" t="n">
-        <v>57950</v>
+        <v>91872</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2403,45 +2411,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Högstaskogen, Srm</t>
+          <t>A 59566-2025, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>684961</v>
+        <v>684983</v>
       </c>
       <c r="R17" t="n">
-        <v>6562439</v>
+        <v>6562551</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2465,17 +2465,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Bearbetad granlåga, fullt av hackspån.</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2490,24 +2485,24 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130009797</t>
+          <t>https://artportalen.se/Sighting/130121578</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130114980</v>
+        <v>130009797</v>
       </c>
       <c r="B18" t="n">
         <v>57950</v>
@@ -2535,11 +2530,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
@@ -2550,17 +2541,17 @@
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lingonliden2, Srm</t>
+          <t>Högstaskogen, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>684878</v>
+        <v>684961</v>
       </c>
       <c r="R18" t="n">
-        <v>6562610</v>
+        <v>6562439</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2584,22 +2575,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>11:31</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>11:31</t>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Bearbetad granlåga, fullt av hackspån.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2614,24 +2600,24 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130114980</t>
+          <t>https://artportalen.se/Sighting/130009797</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130114997</v>
+        <v>130114980</v>
       </c>
       <c r="B19" t="n">
         <v>57950</v>
@@ -2674,14 +2660,14 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lingonliden2, Lingonliden2, Srm</t>
+          <t>Lingonliden2, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>684941</v>
+        <v>684878</v>
       </c>
       <c r="R19" t="n">
-        <v>6562537</v>
+        <v>6562610</v>
       </c>
       <c r="S19" t="n">
         <v>8</v>
@@ -2713,7 +2699,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2723,7 +2709,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2749,13 +2735,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130114997</t>
+          <t>https://artportalen.se/Sighting/130114980</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130121529</v>
+        <v>130114997</v>
       </c>
       <c r="B20" t="n">
         <v>57950</v>
@@ -2783,25 +2769,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>S Tyresta by, Srm</t>
+          <t>Lingonliden2, Lingonliden2, Srm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>685144</v>
+        <v>684941</v>
       </c>
       <c r="R20" t="n">
-        <v>6562346</v>
+        <v>6562537</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2830,7 +2823,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:17</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2840,12 +2833,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:17</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Födosökshack vid basen av död stående tall.</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2860,24 +2848,24 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130121529</t>
+          <t>https://artportalen.se/Sighting/130114997</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130121540</v>
+        <v>130121529</v>
       </c>
       <c r="B21" t="n">
         <v>57950</v>
@@ -2917,10 +2905,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>684954</v>
+        <v>685144</v>
       </c>
       <c r="R21" t="n">
-        <v>6562574</v>
+        <v>6562346</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2952,7 +2940,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2962,7 +2950,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -2993,16 +2981,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130121540</t>
+          <t>https://artportalen.se/Sighting/130121529</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130121542</v>
+        <v>130121540</v>
       </c>
       <c r="B22" t="n">
-        <v>4775</v>
+        <v>57950</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3010,27 +2998,27 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100299</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3039,10 +3027,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>684957</v>
+        <v>684954</v>
       </c>
       <c r="R22" t="n">
-        <v>6562562</v>
+        <v>6562574</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3074,7 +3062,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3084,7 +3072,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Födosökshack vid basen av död stående tall.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3095,21 +3088,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3125,13 +3103,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130121542</t>
+          <t>https://artportalen.se/Sighting/130121540</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130121544</v>
+        <v>130121542</v>
       </c>
       <c r="B23" t="n">
         <v>4775</v>
@@ -3171,10 +3149,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>684893</v>
+        <v>684957</v>
       </c>
       <c r="R23" t="n">
-        <v>6562601</v>
+        <v>6562562</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3206,7 +3184,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3216,7 +3194,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3257,16 +3235,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130121544</t>
+          <t>https://artportalen.se/Sighting/130121542</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130121543</v>
+        <v>130121544</v>
       </c>
       <c r="B24" t="n">
-        <v>5179</v>
+        <v>4775</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3274,21 +3252,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3303,10 +3281,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>684897</v>
+        <v>684893</v>
       </c>
       <c r="R24" t="n">
-        <v>6562616</v>
+        <v>6562601</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3338,7 +3316,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3348,7 +3326,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3389,16 +3367,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130121543</t>
+          <t>https://artportalen.se/Sighting/130121544</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130115019</v>
+        <v>130121543</v>
       </c>
       <c r="B25" t="n">
-        <v>58327</v>
+        <v>5179</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3406,49 +3384,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103015</v>
+        <v>100526</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lingonliden2, Srm</t>
+          <t>S Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>684878</v>
+        <v>684897</v>
       </c>
       <c r="R25" t="n">
-        <v>6562610</v>
+        <v>6562616</v>
       </c>
       <c r="S25" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3477,7 +3448,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3487,7 +3458,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3498,77 +3469,96 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130115019</t>
+          <t>https://artportalen.se/Sighting/130121543</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129996772</v>
+        <v>130115019</v>
       </c>
       <c r="B26" t="n">
-        <v>58114</v>
+        <v>58327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Högstaskogen, Srm</t>
+          <t>Lingonliden2, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>684910</v>
+        <v>684878</v>
       </c>
       <c r="R26" t="n">
-        <v>6562543</v>
+        <v>6562610</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3592,12 +3582,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3612,24 +3612,24 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129996772</t>
+          <t>https://artportalen.se/Sighting/130115019</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130115016</v>
+        <v>129996772</v>
       </c>
       <c r="B27" t="n">
         <v>58114</v>
@@ -3657,32 +3657,28 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lingonliden2, Srm</t>
+          <t>Högstaskogen, Srm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>684878</v>
+        <v>684910</v>
       </c>
       <c r="R27" t="n">
-        <v>6562610</v>
+        <v>6562543</v>
       </c>
       <c r="S27" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3706,22 +3702,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>11:02</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>11:02</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3736,24 +3722,24 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130115016</t>
+          <t>https://artportalen.se/Sighting/129996772</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130328801</v>
+        <v>130115016</v>
       </c>
       <c r="B28" t="n">
         <v>58114</v>
@@ -3781,28 +3767,32 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Högstaskogen, Srm</t>
+          <t>Lingonliden2, Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>684955</v>
+        <v>684878</v>
       </c>
       <c r="R28" t="n">
-        <v>6562389</v>
+        <v>6562610</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3826,12 +3816,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-12-28</t>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3846,27 +3846,27 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130328801</t>
+          <t>https://artportalen.se/Sighting/130115016</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134179933</v>
+        <v>130328801</v>
       </c>
       <c r="B29" t="n">
-        <v>58136</v>
+        <v>58114</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
@@ -3906,13 +3906,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>684976</v>
+        <v>684955</v>
       </c>
       <c r="R29" t="n">
-        <v>6562378</v>
+        <v>6562389</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3936,12 +3936,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2025-12-28</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3967,13 +3967,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134179933</t>
+          <t>https://artportalen.se/Sighting/130328801</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134180019</v>
+        <v>134179933</v>
       </c>
       <c r="B30" t="n">
         <v>58136</v>
@@ -4016,10 +4016,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>685035</v>
+        <v>684976</v>
       </c>
       <c r="R30" t="n">
-        <v>6562398</v>
+        <v>6562378</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4077,63 +4077,62 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134180019</t>
+          <t>https://artportalen.se/Sighting/134179933</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130114978</v>
+        <v>134180019</v>
       </c>
       <c r="B31" t="n">
-        <v>8455</v>
+        <v>58136</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lingonliden2, Lingonliden2, Srm</t>
+          <t>Högstaskogen, Srm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>685149</v>
+        <v>685035</v>
       </c>
       <c r="R31" t="n">
-        <v>6562238</v>
+        <v>6562398</v>
       </c>
       <c r="S31" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4157,22 +4156,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>14:04</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>14:04</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4187,24 +4176,24 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth, Irena Koelemeijer</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130114978</t>
+          <t>https://artportalen.se/Sighting/134180019</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130121530</v>
+        <v>130114978</v>
       </c>
       <c r="B32" t="n">
         <v>8455</v>
@@ -4232,25 +4221,29 @@
           <t>(Hartig, 1834)</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>S Tyresta by, Srm</t>
+          <t>Lingonliden2, Lingonliden2, Srm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>685150</v>
+        <v>685149</v>
       </c>
       <c r="R32" t="n">
-        <v>6562245</v>
+        <v>6562238</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4279,7 +4272,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4289,7 +4282,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4300,48 +4293,28 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL32" t="inlineStr">
-        <is>
-          <t>Tallåga</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Tallåga</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Anneli Ahlroth, Irena Koelemeijer</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130121530</t>
+          <t>https://artportalen.se/Sighting/130114978</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130121533</v>
+        <v>130121530</v>
       </c>
       <c r="B33" t="n">
         <v>8455</v>
@@ -4381,10 +4354,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>684997</v>
+        <v>685150</v>
       </c>
       <c r="R33" t="n">
-        <v>6562386</v>
+        <v>6562245</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4416,7 +4389,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4426,7 +4399,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4450,12 +4423,12 @@
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>På gren på barklös tallåga från äldre tall.</t>
+          <t>Tallåga</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Pinus sylvestris # På gren på barklös tallåga från äldre tall.</t>
+          <t>Pinus sylvestris # Tallåga</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4472,13 +4445,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130121533</t>
+          <t>https://artportalen.se/Sighting/130121530</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130330908</v>
+        <v>130121533</v>
       </c>
       <c r="B34" t="n">
         <v>8455</v>
@@ -4507,25 +4480,21 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
           <t>äldre gnagspår</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Skogen söder om Tyresta by, Srm</t>
+          <t>S Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>684899</v>
+        <v>684997</v>
       </c>
       <c r="R34" t="n">
-        <v>6562614</v>
+        <v>6562386</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4552,12 +4521,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-12-27</t>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4566,34 +4545,53 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL34" t="inlineStr">
+        <is>
+          <t>På gren på barklös tallåga från äldre tall.</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # På gren på barklös tallåga från äldre tall.</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Björn Persson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Björn Persson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130330908</t>
+          <t>https://artportalen.se/Sighting/130121533</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>116794459</v>
+        <v>130330908</v>
       </c>
       <c r="B35" t="n">
-        <v>56884</v>
+        <v>8455</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4601,43 +4599,43 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>208255</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Högstaskogen, Srm</t>
+          <t>Skogen söder om Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>684898</v>
+        <v>684899</v>
       </c>
       <c r="R35" t="n">
-        <v>6562545</v>
+        <v>6562614</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4664,12 +4662,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2025-12-27</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-05-10</t>
+          <t>2025-12-27</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4685,27 +4683,27 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Björn Persson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Björn Persson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/116794459</t>
+          <t>https://artportalen.se/Sighting/130330908</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127378764</v>
+        <v>116794459</v>
       </c>
       <c r="B36" t="n">
-        <v>56876</v>
+        <v>56884</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4713,21 +4711,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>208257</v>
+        <v>208255</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4746,10 +4744,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>684991</v>
+        <v>684898</v>
       </c>
       <c r="R36" t="n">
-        <v>6562475</v>
+        <v>6562545</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4776,12 +4774,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2024-05-10</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-08-10</t>
+          <t>2024-05-10</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4808,16 +4806,16 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127378764</t>
+          <t>https://artportalen.se/Sighting/116794459</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133964707</v>
+        <v>127378764</v>
       </c>
       <c r="B37" t="n">
-        <v>56896</v>
+        <v>56876</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4850,11 +4848,7 @@
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>funnen död</t>
-        </is>
-      </c>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4862,10 +4856,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>684926</v>
+        <v>684991</v>
       </c>
       <c r="R37" t="n">
-        <v>6562530</v>
+        <v>6562475</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4892,17 +4886,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>På ridvägen med krossat huvud.</t>
+          <t>2025-08-10</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4929,13 +4918,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133964707</t>
+          <t>https://artportalen.se/Sighting/127378764</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>134003472</v>
+        <v>133964707</v>
       </c>
       <c r="B38" t="n">
         <v>56896</v>
@@ -4971,7 +4960,11 @@
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>funnen död</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4979,10 +4972,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>684886</v>
+        <v>684926</v>
       </c>
       <c r="R38" t="n">
-        <v>6562537</v>
+        <v>6562530</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5009,17 +5002,17 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>På ridvägen.</t>
+          <t>På ridvägen med krossat huvud.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5046,16 +5039,16 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134003472</t>
+          <t>https://artportalen.se/Sighting/133964707</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133965707</v>
+        <v>134003472</v>
       </c>
       <c r="B39" t="n">
-        <v>98219</v>
+        <v>56896</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5063,38 +5056,43 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>219815</v>
+        <v>208257</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ekbräken</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Gymnocarpium dryopteris</t>
+          <t>Anguis fragilis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Newman</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>N Övre Hammarby, Srm</t>
+          <t>Högstaskogen, Srm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>685126</v>
+        <v>684886</v>
       </c>
       <c r="R39" t="n">
-        <v>6562254</v>
+        <v>6562537</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5121,12 +5119,17 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>På ridvägen.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5153,16 +5156,16 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133965707</t>
+          <t>https://artportalen.se/Sighting/134003472</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>115521263</v>
+        <v>133965707</v>
       </c>
       <c r="B40" t="n">
-        <v>106244</v>
+        <v>98219</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5170,21 +5173,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221144</v>
+        <v>219815</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Newman</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5194,14 +5197,14 @@
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Högstaskogen, Srm</t>
+          <t>N Övre Hammarby, Srm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>684827</v>
+        <v>685126</v>
       </c>
       <c r="R40" t="n">
-        <v>6562598</v>
+        <v>6562254</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5228,12 +5231,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5260,16 +5263,16 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115521263</t>
+          <t>https://artportalen.se/Sighting/133965707</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130121584</v>
+        <v>115521263</v>
       </c>
       <c r="B41" t="n">
-        <v>106243</v>
+        <v>106244</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5296,26 +5299,22 @@
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>A 59566-2025, Srm</t>
+          <t>Högstaskogen, Srm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>685013</v>
+        <v>684827</v>
       </c>
       <c r="R41" t="n">
-        <v>6562405</v>
+        <v>6562598</v>
       </c>
       <c r="S41" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5339,17 +5338,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Flera plantor</t>
+          <t>2024-03-23</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5365,27 +5359,27 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130121584</t>
+          <t>https://artportalen.se/Sighting/115521263</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>134440544</v>
+        <v>130121584</v>
       </c>
       <c r="B42" t="n">
-        <v>106324</v>
+        <v>106243</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5414,24 +5408,24 @@
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>N Övre Hammarby, Srm</t>
+          <t>A 59566-2025, Srm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>685174</v>
+        <v>685013</v>
       </c>
       <c r="R42" t="n">
-        <v>6562279</v>
+        <v>6562405</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5455,17 +5449,17 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2025-12-13</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ett flertal plantor varav två med blomstänglar.</t>
+          <t>Flera plantor</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5481,24 +5475,24 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134440544</t>
+          <t>https://artportalen.se/Sighting/130121584</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>134440598</v>
+        <v>134440544</v>
       </c>
       <c r="B43" t="n">
         <v>106324</v>
@@ -5530,7 +5524,7 @@
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>knoppbristning</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
@@ -5541,10 +5535,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>685131</v>
+        <v>685174</v>
       </c>
       <c r="R43" t="n">
-        <v>6562317</v>
+        <v>6562279</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5581,7 +5575,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ett flertal plantor varav en med blomstängel.</t>
+          <t>Ett flertal plantor varav två med blomstänglar.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5608,16 +5602,16 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134440598</t>
+          <t>https://artportalen.se/Sighting/134440544</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130121531</v>
+        <v>134440598</v>
       </c>
       <c r="B44" t="n">
-        <v>97983</v>
+        <v>106324</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5625,34 +5619,42 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221945</v>
+        <v>221144</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>knoppbristning</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>S Tyresta by, Srm</t>
+          <t>N Övre Hammarby, Srm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>685093</v>
+        <v>685131</v>
       </c>
       <c r="R44" t="n">
-        <v>6562301</v>
+        <v>6562317</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5679,22 +5681,17 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>13:53</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>13:53</t>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ett flertal plantor varav en med blomstängel.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5703,33 +5700,34 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130121531</t>
+          <t>https://artportalen.se/Sighting/134440598</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130110447</v>
+        <v>130121531</v>
       </c>
       <c r="B45" t="n">
-        <v>97986</v>
+        <v>97983</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5737,16 +5735,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5757,14 +5755,14 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Tyresta, Tyresta, Srm</t>
+          <t>S Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>684940</v>
+        <v>685093</v>
       </c>
       <c r="R45" t="n">
-        <v>6562551</v>
+        <v>6562301</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5794,9 +5792,19 @@
           <t>2025-12-13</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5811,24 +5819,24 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130110447</t>
+          <t>https://artportalen.se/Sighting/130121531</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130115022</v>
+        <v>130110447</v>
       </c>
       <c r="B46" t="n">
         <v>97986</v>
@@ -5857,23 +5865,19 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lingonliden2, Srm</t>
+          <t>Tyresta, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>684878</v>
+        <v>684940</v>
       </c>
       <c r="R46" t="n">
-        <v>6562610</v>
+        <v>6562551</v>
       </c>
       <c r="S46" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5900,19 +5904,9 @@
           <t>2025-12-13</t>
         </is>
       </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>11:22</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>11:22</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5927,27 +5921,27 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anneli Ahlroth</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/130115022</t>
+          <t>https://artportalen.se/Sighting/130110447</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133965744</v>
+        <v>130115022</v>
       </c>
       <c r="B47" t="n">
-        <v>98249</v>
+        <v>97986</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5955,21 +5949,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>223358</v>
+        <v>221946</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5979,17 +5973,17 @@
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>N Övre Hammarby, Srm</t>
+          <t>Lingonliden2, Srm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>685126</v>
+        <v>684878</v>
       </c>
       <c r="R47" t="n">
-        <v>6562254</v>
+        <v>6562610</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6013,12 +6007,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6027,69 +6031,72 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Anneli Ahlroth</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133965744</t>
+          <t>https://artportalen.se/Sighting/130115022</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130121534</v>
+        <v>133965744</v>
       </c>
       <c r="B48" t="n">
-        <v>92328</v>
+        <v>98249</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6040162</v>
+        <v>223358</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tallkötticka</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>S Tyresta by, Srm</t>
+          <t>N Övre Hammarby, Srm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>684997</v>
+        <v>685126</v>
       </c>
       <c r="R48" t="n">
-        <v>6562398</v>
+        <v>6562254</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6116,22 +6123,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>13:45</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-12-13</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>13:45</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6140,42 +6137,155 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL48" t="inlineStr">
-        <is>
-          <t>På gren på barklös tallåga från äldre tall.</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # På gren på barklös tallåga från äldre tall.</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Birgitta Tulin, Irena Koelemeijer, Ulla Sebestyen</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133965744</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>130121534</v>
+      </c>
+      <c r="B49" t="n">
+        <v>92328</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6040162</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Tallkötticka</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Leptoporus erubescens</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>S Tyresta by, Srm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>684997</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6562398</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-12-13</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL49" t="inlineStr">
+        <is>
+          <t>På gren på barklös tallåga från äldre tall.</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # På gren på barklös tallåga från äldre tall.</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Birgitta Tulin, Irena Koelemeijer, Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/130121534</t>
         </is>
@@ -6230,6 +6340,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 59566-2025 artfynd.xlsx
+++ b/artfynd/A 59566-2025 artfynd.xlsx
@@ -1616,7 +1616,7 @@
         <v>135324359</v>
       </c>
       <c r="B10" t="n">
-        <v>91531</v>
+        <v>91533</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
